--- a/CryoGrid/CryoGridCommunity_results/test_x/test_x.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/test_x/test_x.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_Optimization_Automatization_Workflow-main\CryoGrid\CryoGridCommunity_results\test_x\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\test_x\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4EFA8E-97FC-4635-BCF8-E4F7F82248D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B905C4F-7C48-40AF-9133-342C998E1185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" xr2:uid="{7F391892-6F91-4B79-994F-B6C44A501F95}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A8AAC819-E91F-4A51-B670-BB34F60E0265}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="101">
   <si>
     <t>-------------------</t>
   </si>
@@ -141,6 +141,204 @@
   </si>
   <si>
     <t>area of target point in m2</t>
+  </si>
+  <si>
+    <t>TILE</t>
+  </si>
+  <si>
+    <t>TILE_1D_standard2</t>
+  </si>
+  <si>
+    <t>domain_depth</t>
+  </si>
+  <si>
+    <t>vertical depth of the model domain [m]</t>
+  </si>
+  <si>
+    <t>forcing_class</t>
+  </si>
+  <si>
+    <t>FORCING_seb</t>
+  </si>
+  <si>
+    <t>forcing_class_index</t>
+  </si>
+  <si>
+    <t>grid_class</t>
+  </si>
+  <si>
+    <t>GRID_user_defined</t>
+  </si>
+  <si>
+    <t>grid_class_index</t>
+  </si>
+  <si>
+    <t>out_class</t>
+  </si>
+  <si>
+    <t>OUT_all_lateral</t>
+  </si>
+  <si>
+    <t>out_class_index</t>
+  </si>
+  <si>
+    <t>strat_classes_class</t>
+  </si>
+  <si>
+    <t>STRAT_classes</t>
+  </si>
+  <si>
+    <t>strat_classes_class_index</t>
+  </si>
+  <si>
+    <t>strat_statvar_class</t>
+  </si>
+  <si>
+    <t>STRAT_layers</t>
+  </si>
+  <si>
+    <t>STRAT_linear</t>
+  </si>
+  <si>
+    <t>list of STRATIGRAPHY_STATVAR classes that provide initial state of state variables</t>
+  </si>
+  <si>
+    <t>strat_statvar_class_index</t>
+  </si>
+  <si>
+    <t>lateral_class</t>
+  </si>
+  <si>
+    <t>LATERAL_1D</t>
+  </si>
+  <si>
+    <t>lateral class, e.g. LATERAL1D or LATERAL3D</t>
+  </si>
+  <si>
+    <t>lateral_class_index</t>
+  </si>
+  <si>
+    <t>lateral_IA_classes</t>
+  </si>
+  <si>
+    <t>list of lateral interaction classes</t>
+  </si>
+  <si>
+    <t>lateral_IA_classes_index</t>
+  </si>
+  <si>
+    <t>restart_file_path</t>
+  </si>
+  <si>
+    <t>path and filename of restart file</t>
+  </si>
+  <si>
+    <t>restart_file_name</t>
+  </si>
+  <si>
+    <t>FORCING</t>
+  </si>
+  <si>
+    <t>FORCING_seb_mat</t>
+  </si>
+  <si>
+    <t>filename</t>
+  </si>
+  <si>
+    <t>filename of Matlab file containing forcing data</t>
+  </si>
+  <si>
+    <t>forcing_path</t>
+  </si>
+  <si>
+    <t>../CryoGridCommunity_forcing/</t>
+  </si>
+  <si>
+    <t>path where forcing data file is located</t>
+  </si>
+  <si>
+    <t>start_time</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>start time of the simulations (must be within the range of data in forcing file) - year month day</t>
+  </si>
+  <si>
+    <t>end_time</t>
+  </si>
+  <si>
+    <t>end_time time of the simulations (must be within the range of data in forcing file) - year month day</t>
+  </si>
+  <si>
+    <t>rain_fraction</t>
+  </si>
+  <si>
+    <t>rainfall fraction assumed in simulations (rainfall from the forcing data file is multiplied by this parameter)</t>
+  </si>
+  <si>
+    <t>snow_fraction</t>
+  </si>
+  <si>
+    <t>snowfall fraction assumed in simulations (rainfall from the forcing data file is multiplied by this parameter)</t>
+  </si>
+  <si>
+    <t>heatFlux_lb</t>
+  </si>
+  <si>
+    <t>heat flux at the lower boundary [W/m2] - positive values correspond to energy gain</t>
+  </si>
+  <si>
+    <t>airT_height</t>
+  </si>
+  <si>
+    <t>height above ground surface where air temperature from forcing data is applied</t>
+  </si>
+  <si>
+    <t>post_proc_class</t>
+  </si>
+  <si>
+    <t>list of postprocessing classes to modify forcing data in user-defined ways; no post-processing applied when empty</t>
+  </si>
+  <si>
+    <t>post_proc_class_index</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>OUT_do_nothing</t>
+  </si>
+  <si>
+    <t>display_timestep</t>
+  </si>
+  <si>
+    <t>timestep that model progress is displayed [days]</t>
+  </si>
+  <si>
+    <t>OUT_last_timestep</t>
+  </si>
+  <si>
+    <t>save_timestep</t>
+  </si>
+  <si>
+    <t>in days, if empty save final state at the end of the run, so that it can serve as initial condition for new runs</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>additional tag added to file name</t>
+  </si>
+  <si>
+    <t>tag2</t>
   </si>
 </sst>
 </file>
@@ -511,8 +709,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0859BA9-BBA8-4F7F-8825-0BA8F17AE4E7}">
-  <dimension ref="A1:H28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6718D10D-20C3-4FE7-9B2D-BE2221519AB8}">
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -641,8 +839,8 @@
       <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>11</v>
+      <c r="B17">
+        <v>78.900000000000006</v>
       </c>
       <c r="C17">
         <v>78.900000000000006</v>
@@ -655,8 +853,8 @@
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" t="s">
-        <v>11</v>
+      <c r="B18">
+        <v>11.1</v>
       </c>
       <c r="C18">
         <v>11.1</v>
@@ -669,8 +867,8 @@
       <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
-        <v>11</v>
+      <c r="B19">
+        <v>10</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -683,8 +881,8 @@
       <c r="A20" t="s">
         <v>24</v>
       </c>
-      <c r="B20" t="s">
-        <v>11</v>
+      <c r="B20">
+        <v>10</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -697,8 +895,8 @@
       <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="B21" t="s">
-        <v>11</v>
+      <c r="B21">
+        <v>180</v>
       </c>
       <c r="C21">
         <v>180</v>
@@ -769,8 +967,8 @@
       <c r="A27" t="s">
         <v>33</v>
       </c>
-      <c r="B27" t="s">
-        <v>11</v>
+      <c r="B27">
+        <v>1</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -781,6 +979,696 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>100</v>
+      </c>
+      <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>47</v>
+      </c>
+      <c r="B69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>68</v>
+      </c>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>70</v>
+      </c>
+      <c r="B78" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" t="s">
+        <v>71</v>
+      </c>
+      <c r="D78" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>73</v>
+      </c>
+      <c r="B79" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" t="s">
+        <v>74</v>
+      </c>
+      <c r="D79" t="s">
+        <v>75</v>
+      </c>
+      <c r="E79" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" t="s">
+        <v>74</v>
+      </c>
+      <c r="D80" t="s">
+        <v>75</v>
+      </c>
+      <c r="E80" t="s">
+        <v>76</v>
+      </c>
+      <c r="F80" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83">
+        <v>0.05</v>
+      </c>
+      <c r="C83">
+        <v>0.05</v>
+      </c>
+      <c r="D83" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84">
+        <v>2</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>5</v>
+      </c>
+      <c r="C94">
+        <v>5</v>
+      </c>
+      <c r="D94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>91</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>95</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C101" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>96</v>
+      </c>
+      <c r="D102" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>98</v>
+      </c>
+      <c r="D103" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>100</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>91</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>95</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>96</v>
+      </c>
+      <c r="D112" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>98</v>
+      </c>
+      <c r="D113" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>100</v>
+      </c>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>14</v>
       </c>
     </row>
